--- a/Mystical_Beasts_Alliance_WORK_LOG_v3.xlsx
+++ b/Mystical_Beasts_Alliance_WORK_LOG_v3.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P500"/>
+  <dimension ref="A1:Q500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -593,6 +594,11 @@
       <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Inventory Status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>รูปการทำงาน</t>
         </is>
       </c>
     </row>

--- a/Mystical_Beasts_Alliance_WORK_LOG_v3.xlsx
+++ b/Mystical_Beasts_Alliance_WORK_LOG_v3.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INVENTORY LOG" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORK LOG ITEMS" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORK LOG LISTS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DELETION REQUESTS" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="CategoryList">'WORK LOG LISTS'!$A$2:$A$3</definedName>
@@ -41,7 +42,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +60,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -128,6 +137,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15594,6 +15604,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Request ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Requested At</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Work ID</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>ผู้ขอลบ</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>เหตุผล</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Approved At</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Approved By</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Mystical_Beasts_Alliance_WORK_LOG_v3.xlsx
+++ b/Mystical_Beasts_Alliance_WORK_LOG_v3.xlsx
@@ -16,7 +16,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INVENTORY LOG" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORK LOG ITEMS" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORK LOG LISTS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DELETION REQUESTS" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="CategoryList">'WORK LOG LISTS'!$A$2:$A$3</definedName>
@@ -42,7 +41,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,14 +59,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -105,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,7 +128,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15604,62 +15594,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Request ID</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>Requested At</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>Work ID</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>ผู้ขอลบ</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>เหตุผล</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G1" s="13" t="inlineStr">
-        <is>
-          <t>Approved At</t>
-        </is>
-      </c>
-      <c r="H1" s="13" t="inlineStr">
-        <is>
-          <t>Approved By</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
